--- a/data/trans_dic/P57B3_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P57B3_R-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,22; 16,25</t>
+          <t>11,17; 16,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,03; 17,43</t>
+          <t>13,28; 17,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,74; 16,04</t>
+          <t>12,93; 16,39</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,92; 67,0</t>
+          <t>10,73; 14,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,68; 17,74</t>
+          <t>14,08; 18,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,03; 49,35</t>
+          <t>12,92; 15,75</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,25; 11,78</t>
+          <t>7,23; 11,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,29; 9,52</t>
+          <t>7,5; 11,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,17; 9,78</t>
+          <t>7,68; 10,63</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,26; 12,99</t>
+          <t>10,07; 13,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,04; 13,4</t>
+          <t>11,53; 14,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,84; 12,67</t>
+          <t>11,32; 13,91</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,97; 37,04</t>
+          <t>10,71; 13,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,8; 13,21</t>
+          <t>12,62; 14,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,54; 26,32</t>
+          <t>12,02; 13,44</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>85937</t>
+          <t>93564</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>101963</t>
+          <t>111677</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>187899</t>
+          <t>205241</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>71293; 103287</t>
+          <t>77178; 113629</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>87866; 117466</t>
+          <t>97128; 126484</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>166856; 210109</t>
+          <t>183810; 233015</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>356620</t>
+          <t>132796</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>147631</t>
+          <t>171225</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>504252</t>
+          <t>304021</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>130198; 798581</t>
+          <t>112450; 153786</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>130958; 169754</t>
+          <t>150621; 193211</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>280092; 1060418</t>
+          <t>273643; 333396</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>64399</t>
+          <t>71994</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64584</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>128983</t>
+          <t>146994</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>51014; 82941</t>
+          <t>58002; 90125</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30702; 88747</t>
+          <t>60798; 91580</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>84658; 159947</t>
+          <t>123894; 171490</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>102378</t>
+          <t>118686</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>126312</t>
+          <t>146904</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>228690</t>
+          <t>265590</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>85864; 120401</t>
+          <t>99717; 137866</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>98798; 146411</t>
+          <t>128735; 166602</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>198649; 255992</t>
+          <t>238584; 293083</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>609334</t>
+          <t>417039</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>440490</t>
+          <t>504807</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1049824</t>
+          <t>921846</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>379463; 1280857</t>
+          <t>378278; 460031</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>358236; 482937</t>
+          <t>470570; 542857</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>820712; 1872786</t>
+          <t>872490; 975451</t>
         </is>
       </c>
     </row>
